--- a/PPREstimation/output/top10/47_1_East_China_Sea_(1997).xlsx
+++ b/PPREstimation/output/top10/47_1_East_China_Sea_(1997).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -701,7 +700,6 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>3.813643593695144</v>
       </c>
@@ -869,7 +866,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>4.081369216765723</v>
       </c>
@@ -953,7 +949,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
         <v>3.146723685909917</v>
       </c>
@@ -1037,7 +1032,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
         <v>3.390382324723566</v>
       </c>
@@ -1121,7 +1115,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
         <v>3.13932907764769</v>
       </c>
@@ -1205,7 +1198,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
         <v>3.13873617353427</v>
       </c>
@@ -1289,7 +1281,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
         <v>3.098580953503004</v>
       </c>
@@ -1373,7 +1364,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>2.958320591355371</v>
       </c>
@@ -1457,7 +1447,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
         <v>3.772674520514855</v>
       </c>
@@ -1541,7 +1530,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
         <v>3.206991188715405</v>
       </c>
@@ -1625,7 +1613,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
         <v>3.508809514410474</v>
       </c>
@@ -1709,7 +1696,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
         <v>2.846936152547148</v>
       </c>
@@ -1793,7 +1779,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
         <v>3.007323841230849</v>
       </c>
@@ -1877,7 +1862,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
         <v>2.819131829142155</v>
       </c>
@@ -1961,7 +1945,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
         <v>2.314</v>
       </c>
@@ -2045,7 +2028,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
         <v>2.322264264264264</v>
       </c>
@@ -2129,7 +2111,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
         <v>2</v>
       </c>
@@ -2213,7 +2194,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
         <v>2.220235336464297</v>
       </c>
@@ -2297,7 +2277,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
         <v>2.161129032258064</v>
       </c>
@@ -2381,7 +2360,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
         <v>2.169354838709677</v>
       </c>
@@ -2465,7 +2443,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
         <v>2</v>
       </c>
@@ -2549,7 +2526,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
         <v>2</v>
       </c>
@@ -2633,7 +2609,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
@@ -2709,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2847,6 +2822,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2857,9 +2842,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -2890,19 +2872,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2915,9 +2897,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -2967,6 +2946,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2979,11 +2961,8 @@
           <t>Marine mammals</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>1.634213823397891</v>
+        <v>974.1354169426057</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -2991,7 +2970,6 @@
       <c r="H4" s="2" t="n">
         <v>80.71108849938453</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -3030,6 +3008,9 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>434.1112192505759</v>
       </c>
     </row>
     <row r="5">
@@ -3041,11 +3022,8 @@
           <t>Sharks</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>1.476724928703378</v>
+        <v>1517.91026006447</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -3053,7 +3031,6 @@
       <c r="H5" s="2" t="n">
         <v>90.9091558140732</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
@@ -3092,6 +3069,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>634.3962916200602</v>
       </c>
     </row>
     <row r="6">
@@ -3103,11 +3083,8 @@
           <t>Small yellow croakers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>1.330830967362291</v>
+        <v>181.3544760060738</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>169.1028250414846</v>
@@ -3156,6 +3133,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>197.1521708332211</v>
+      </c>
+      <c r="X6" t="n">
+        <v>95.97283283614445</v>
       </c>
     </row>
     <row r="7">
@@ -3167,11 +3147,8 @@
           <t>Large yellow croakers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>1.065872231548243</v>
+        <v>294.959605983177</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>32.36152056671166</v>
@@ -3220,6 +3197,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>34.5723010017227</v>
+      </c>
+      <c r="X7" t="n">
+        <v>148.6408705033719</v>
       </c>
     </row>
     <row r="8">
@@ -3231,11 +3211,8 @@
           <t>Omnivores</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>1.193784340427056</v>
+        <v>163.1386748285371</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>39.15119708788369</v>
@@ -3284,6 +3261,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>45.58552524511551</v>
+      </c>
+      <c r="X8" t="n">
+        <v>85.78736356835823</v>
       </c>
     </row>
     <row r="9">
@@ -3295,11 +3275,8 @@
           <t>Benthivores/piscivores</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>0.8674397543909175</v>
+        <v>157.7816158923701</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>19.56058723472377</v>
@@ -3348,6 +3325,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>20.70950495529543</v>
+      </c>
+      <c r="X9" t="n">
+        <v>79.90756538743085</v>
       </c>
     </row>
     <row r="10">
@@ -3359,11 +3339,8 @@
           <t>Planktivores/piscivores</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>1.060476713918748</v>
+        <v>99.71717982329827</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>312.2386594768244</v>
@@ -3412,6 +3389,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>408.7365245990336</v>
+      </c>
+      <c r="X10" t="n">
+        <v>56.03831183777037</v>
       </c>
     </row>
     <row r="11">
@@ -3423,11 +3403,8 @@
           <t>Planktivores/Benthivores</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>1.335670261405361</v>
+        <v>76.09816436589465</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>86.85346284260763</v>
@@ -3476,6 +3453,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>89.08845942790761</v>
+      </c>
+      <c r="X11" t="n">
+        <v>47.43001081882673</v>
       </c>
     </row>
     <row r="12">
@@ -3487,11 +3467,8 @@
           <t>Bombay duck</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>1.532986826364916</v>
+        <v>527.4219661820977</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>113.1327190470715</v>
@@ -3540,6 +3517,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>198.2334553573471</v>
+      </c>
+      <c r="X12" t="n">
+        <v>262.6167809333608</v>
       </c>
     </row>
     <row r="13">
@@ -3551,11 +3531,8 @@
           <t>Hairtails</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>1.251805686809552</v>
+        <v>208.6937247005938</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>147.2850928817751</v>
@@ -3604,6 +3581,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>254.9943541742523</v>
+      </c>
+      <c r="X13" t="n">
+        <v>103.810376670963</v>
       </c>
     </row>
     <row r="14">
@@ -3615,11 +3595,8 @@
           <t>Piscivores</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>1.498127004028522</v>
+        <v>537.641910555065</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>163.8502289148532</v>
@@ -3668,6 +3645,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>187.5890422077808</v>
+      </c>
+      <c r="X14" t="n">
+        <v>254.1297863946551</v>
       </c>
     </row>
     <row r="15">
@@ -3679,11 +3659,8 @@
           <t>Benthivores</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>0.507880594070187</v>
+        <v>80.56053103238106</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>15.39708914107206</v>
@@ -3732,6 +3709,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>21.50577968905311</v>
+      </c>
+      <c r="X15" t="n">
+        <v>42.40377922555103</v>
       </c>
     </row>
     <row r="16">
@@ -3743,11 +3723,8 @@
           <t>Planktivores</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>1.333041719327266</v>
+        <v>78.07551688990829</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>37.00920130873283</v>
@@ -3796,6 +3773,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>39.08227484843405</v>
+      </c>
+      <c r="X16" t="n">
+        <v>48.59471740352376</v>
       </c>
     </row>
     <row r="17">
@@ -3807,11 +3787,8 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>1.261677900660831</v>
+        <v>76.64475742175614</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>26.77963225521344</v>
@@ -3860,6 +3837,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>28.03948019878493</v>
+      </c>
+      <c r="X17" t="n">
+        <v>46.24790849062932</v>
       </c>
     </row>
     <row r="18">
@@ -3871,11 +3851,8 @@
           <t>Shrimps</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>0.4726706495332721</v>
+        <v>16.53433243207267</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>7.18476765535589</v>
@@ -3924,6 +3901,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>7.65504524769725</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.62200656965605</v>
       </c>
     </row>
     <row r="19">
@@ -3935,11 +3915,8 @@
           <t>Crabs</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>0.5049798544422613</v>
+        <v>14.70593870822873</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5.117943567052834</v>
@@ -3988,6 +3965,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>5.078557688490925</v>
+      </c>
+      <c r="X19" t="n">
+        <v>9.517715288238174</v>
       </c>
     </row>
     <row r="20">
@@ -3999,11 +3979,8 @@
           <t>Other invertebrates</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>0.8344138253677151</v>
+        <v>6.308737502636358</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>8.766233766233766</v>
@@ -4052,6 +4029,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>8.751026427609757</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.993354874061211</v>
       </c>
     </row>
     <row r="21">
@@ -4063,11 +4043,8 @@
           <t>Echinoderms</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>0.8915136012295339</v>
+        <v>14.15589660156355</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>25.47086624110775</v>
@@ -4116,6 +4093,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>579.3710845183947</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9.585148652454038</v>
       </c>
     </row>
     <row r="22">
@@ -4127,11 +4107,8 @@
           <t>Benthic Crustaceans</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>0.4131282106151952</v>
+        <v>9.804105720556635</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>5.357340279389317</v>
@@ -4180,6 +4157,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>5.714341032911785</v>
+      </c>
+      <c r="X22" t="n">
+        <v>6.240516363768144</v>
       </c>
     </row>
     <row r="23">
@@ -4191,11 +4171,8 @@
           <t>Mollusks</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>0.3866371582064311</v>
+        <v>6.856515324482135</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>5.936060606060603</v>
@@ -4244,6 +4221,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>6.573537937068823</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.678878236475726</v>
       </c>
     </row>
     <row r="24">
@@ -4255,9 +4235,6 @@
           <t>Polychaetes</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
@@ -4307,6 +4284,9 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4319,11 +4299,8 @@
           <t>Zooplankton</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>0.9734827962623344</v>
+        <v>7.360193753075751</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>9.090909090909088</v>
@@ -4373,6 +4350,9 @@
       <c r="V25" s="2" t="n">
         <v>9.241787869146691</v>
       </c>
+      <c r="X25" t="n">
+        <v>5.825580686404746</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -4383,9 +4363,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
@@ -4435,6 +4412,9 @@
         <v>1</v>
       </c>
       <c r="V26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4449,7 +4429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4587,6 +4567,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4636,19 +4626,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4721,6 +4714,12 @@
       <c r="V3" s="2" t="n">
         <v>0.863581423884883</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -4738,10 +4737,10 @@
         <v>645.6152668180546</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.526231947702847</v>
+        <v>743.3725364170139</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.552310881795354</v>
+        <v>1581.669044631617</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -4749,7 +4748,6 @@
       <c r="H4" s="2" t="n">
         <v>134.0448103852573</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -4788,6 +4786,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>385.3484377653213</v>
+      </c>
+      <c r="X4" t="n">
+        <v>694.8613275344992</v>
       </c>
     </row>
     <row r="5">
@@ -4806,10 +4810,10 @@
         <v>1154.74406127404</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.745620886349708</v>
+        <v>1346.545392319917</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2.742397058972659</v>
+        <v>2795.1679898988</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -4817,7 +4821,6 @@
       <c r="H5" s="2" t="n">
         <v>152.5838525087105</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
@@ -4856,6 +4859,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>657.9993946906936</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1158.738330044449</v>
       </c>
     </row>
     <row r="6">
@@ -4874,10 +4883,10 @@
         <v>133.4162317020597</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.015552661822765</v>
+        <v>148.4292633657725</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.043652146840019</v>
+        <v>306.7632816327842</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>272.2451910839072</v>
@@ -4926,6 +4935,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>303.1294514165881</v>
+      </c>
+      <c r="W6" t="n">
+        <v>90.30349061011056</v>
+      </c>
+      <c r="X6" t="n">
+        <v>158.5637618491068</v>
       </c>
     </row>
     <row r="7">
@@ -4944,10 +4959,10 @@
         <v>245.3216832284516</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.199289768352338</v>
+        <v>276.5738825673489</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.227315643070162</v>
+        <v>541.167845511507</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>53.22906226641511</v>
@@ -4996,6 +5011,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>53.88647686964453</v>
+      </c>
+      <c r="W7" t="n">
+        <v>158.17338967292</v>
+      </c>
+      <c r="X7" t="n">
+        <v>274.2390544344365</v>
       </c>
     </row>
     <row r="8">
@@ -5014,10 +5035,10 @@
         <v>131.2214628321221</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.010769774893007</v>
+        <v>145.934763157738</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.036133815221473</v>
+        <v>305.8131375419835</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>66.04435652237277</v>
@@ -5066,6 +5087,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>72.85468745680132</v>
+      </c>
+      <c r="W8" t="n">
+        <v>88.9355323547114</v>
+      </c>
+      <c r="X8" t="n">
+        <v>157.3121050517687</v>
       </c>
     </row>
     <row r="9">
@@ -5084,10 +5111,10 @@
         <v>136.1200585562044</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.021353079015081</v>
+        <v>151.5035698395286</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.039787122658536</v>
+        <v>303.3786473154019</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>36.04605460649624</v>
@@ -5136,6 +5163,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>35.76713208410784</v>
+      </c>
+      <c r="W9" t="n">
+        <v>91.98627241058088</v>
+      </c>
+      <c r="X9" t="n">
+        <v>156.6381367062646</v>
       </c>
     </row>
     <row r="10">
@@ -5154,10 +5187,10 @@
         <v>123.0777938483221</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.992401877848456</v>
+        <v>136.6870094092204</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.97781011356031</v>
+        <v>214.4455523094579</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>560.2993113635969</v>
@@ -5206,6 +5239,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>683.8042433207072</v>
+      </c>
+      <c r="W10" t="n">
+        <v>83.84350782998811</v>
+      </c>
+      <c r="X10" t="n">
+        <v>117.3415435141877</v>
       </c>
     </row>
     <row r="11">
@@ -5224,10 +5263,10 @@
         <v>90.84783292746816</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.907611218998285</v>
+        <v>100.2278952561736</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1.912049794749575</v>
+        <v>109.6135735631875</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>124.2711634145906</v>
@@ -5276,6 +5315,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>122.2418878711609</v>
+      </c>
+      <c r="W11" t="n">
+        <v>63.40473856017664</v>
+      </c>
+      <c r="X11" t="n">
+        <v>68.21858054813588</v>
       </c>
     </row>
     <row r="12">
@@ -5294,10 +5339,10 @@
         <v>475.6166446524368</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.418043845374908</v>
+        <v>543.9985064148083</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.223977121357667</v>
+        <v>787.0602871231563</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>163.5507229305759</v>
@@ -5346,6 +5391,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>277.0567414731555</v>
+      </c>
+      <c r="W12" t="n">
+        <v>290.8855760689498</v>
+      </c>
+      <c r="X12" t="n">
+        <v>388.9017364240259</v>
       </c>
     </row>
     <row r="13">
@@ -5364,10 +5415,10 @@
         <v>137.3008427466518</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.023855250548123</v>
+        <v>152.8465647269913</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.935295445357621</v>
+        <v>361.152394173914</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>245.6862001803302</v>
@@ -5416,6 +5467,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>401.6981769955059</v>
+      </c>
+      <c r="W13" t="n">
+        <v>92.72031843302986</v>
+      </c>
+      <c r="X13" t="n">
+        <v>175.5077449530492</v>
       </c>
     </row>
     <row r="14">
@@ -5434,10 +5491,10 @@
         <v>304.3889985193259</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2.268308535570748</v>
+        <v>344.7830174723056</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2.30031387810577</v>
+        <v>857.4862245205563</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>249.2598774472341</v>
@@ -5486,6 +5543,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>274.5189432152974</v>
+      </c>
+      <c r="W14" t="n">
+        <v>192.9094902193581</v>
+      </c>
+      <c r="X14" t="n">
+        <v>398.7731713813679</v>
       </c>
     </row>
     <row r="15">
@@ -5504,10 +5567,10 @@
         <v>67.81478323443531</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.829367805577168</v>
+        <v>74.34147036847325</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.84032986439515</v>
+        <v>212.9757504641147</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>33.98849134059365</v>
@@ -5556,6 +5619,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>42.47474138804216</v>
+      </c>
+      <c r="W15" t="n">
+        <v>48.44624372378618</v>
+      </c>
+      <c r="X15" t="n">
+        <v>113.7580723413437</v>
       </c>
     </row>
     <row r="16">
@@ -5574,10 +5643,10 @@
         <v>100.9976422281052</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.936769695378661</v>
+        <v>111.683135042612</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.931489587955087</v>
+        <v>116.0427417312385</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>53.47979512001307</v>
@@ -5626,6 +5695,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>54.12960093161038</v>
+      </c>
+      <c r="W16" t="n">
+        <v>69.89558431312599</v>
+      </c>
+      <c r="X16" t="n">
+        <v>71.71229834977616</v>
       </c>
     </row>
     <row r="17">
@@ -5644,10 +5719,10 @@
         <v>65.92916907523437</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.821993919117797</v>
+        <v>72.22998071167444</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.839433090076003</v>
+        <v>110.6202611462784</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>38.38234241528252</v>
@@ -5696,6 +5771,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>38.53302950560662</v>
+      </c>
+      <c r="W17" t="n">
+        <v>47.20523047680616</v>
+      </c>
+      <c r="X17" t="n">
+        <v>66.62924255523933</v>
       </c>
     </row>
     <row r="18">
@@ -5714,10 +5795,10 @@
         <v>20.60629913270002</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.542426707515448</v>
+        <v>22.01068943454562</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.561294750439705</v>
+        <v>41.92758162087955</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>15.07517747610315</v>
@@ -5766,6 +5847,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>14.88502614028108</v>
+      </c>
+      <c r="W18" t="n">
+        <v>16.18813855308676</v>
+      </c>
+      <c r="X18" t="n">
+        <v>27.45670287842556</v>
       </c>
     </row>
     <row r="19">
@@ -5784,10 +5871,10 @@
         <v>21.00217458215732</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.546636407292474</v>
+        <v>22.44284957640871</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.565985118979595</v>
+        <v>43.65189164395604</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>12.03947360007721</v>
@@ -5836,6 +5923,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>11.03550640396157</v>
+      </c>
+      <c r="W19" t="n">
+        <v>16.47411256574711</v>
+      </c>
+      <c r="X19" t="n">
+        <v>28.38105109133995</v>
       </c>
     </row>
     <row r="20">
@@ -5854,10 +5947,10 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>14.61038961038961</v>
@@ -5906,6 +5999,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>13.78907039428072</v>
+      </c>
+      <c r="W20" t="n">
+        <v>8.322258123435352</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.322258123435352</v>
       </c>
     </row>
     <row r="21">
@@ -5924,10 +6023,10 @@
         <v>14.36294379407374</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.464712067662454</v>
+        <v>15.22163111138705</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.389743963354619</v>
+        <v>30.52861938538214</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>47.52855886458278</v>
@@ -5976,6 +6075,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>1019.755012995979</v>
+      </c>
+      <c r="W21" t="n">
+        <v>11.6129642773251</v>
+      </c>
+      <c r="X21" t="n">
+        <v>19.55375571375</v>
       </c>
     </row>
     <row r="22">
@@ -5994,10 +6099,10 @@
         <v>14.47911226566293</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.466403022283111</v>
+        <v>15.34743855512961</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.478879268940024</v>
+        <v>33.85698484918524</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>14.95693718745309</v>
@@ -6046,6 +6151,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>14.54977121954716</v>
+      </c>
+      <c r="W22" t="n">
+        <v>11.69937146537998</v>
+      </c>
+      <c r="X22" t="n">
+        <v>21.51396478035683</v>
       </c>
     </row>
     <row r="23">
@@ -6064,10 +6175,10 @@
         <v>14.49740670372631</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.466668256932992</v>
+        <v>15.36725296668693</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1.466496696494247</v>
+        <v>26.43707994906483</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>17.85074670895786</v>
@@ -6116,6 +6227,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>17.941415846944</v>
+      </c>
+      <c r="W23" t="n">
+        <v>11.71297398809445</v>
+      </c>
+      <c r="X23" t="n">
+        <v>18.00571560239192</v>
       </c>
     </row>
     <row r="24">
@@ -6134,10 +6251,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>6.67641459982895</v>
@@ -6186,6 +6303,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>5.835162046220703</v>
+      </c>
+      <c r="W24" t="n">
+        <v>8.322258123435352</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.322258123435352</v>
       </c>
     </row>
     <row r="25">
@@ -6204,10 +6327,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>12.98701298701298</v>
@@ -6257,6 +6380,12 @@
       <c r="V25" s="2" t="n">
         <v>12.66259887840875</v>
       </c>
+      <c r="W25" t="n">
+        <v>8.322258123435352</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8.322258123435351</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -6325,6 +6454,12 @@
         <v>1</v>
       </c>
       <c r="V26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6339,7 +6474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6477,6 +6612,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6526,19 +6671,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6611,6 +6759,12 @@
       <c r="V3" s="2" t="n">
         <v>0.863581423884883</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -6628,10 +6782,10 @@
         <v>645.6152668180546</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.526231947702847</v>
+        <v>743.3725364170139</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.552310881795354</v>
+        <v>1581.669044631617</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -6680,6 +6834,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>385.3484377653213</v>
+      </c>
+      <c r="X4" t="n">
+        <v>694.8613275344992</v>
       </c>
     </row>
     <row r="5">
@@ -6698,10 +6858,10 @@
         <v>1154.74406127404</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.745620886349708</v>
+        <v>1346.545392319917</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2.742397058972659</v>
+        <v>2795.1679898988</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -6750,6 +6910,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>657.9993946906936</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1158.738330044449</v>
       </c>
     </row>
     <row r="6">
@@ -6768,10 +6934,10 @@
         <v>133.4162317020597</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.015552661822765</v>
+        <v>148.4292633657725</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.043652146840019</v>
+        <v>306.7632816327842</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>272.2451910839072</v>
@@ -6820,6 +6986,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>303.1294514165881</v>
+      </c>
+      <c r="W6" t="n">
+        <v>90.30349061011056</v>
+      </c>
+      <c r="X6" t="n">
+        <v>158.5637618491068</v>
       </c>
     </row>
     <row r="7">
@@ -6838,10 +7010,10 @@
         <v>245.3216832284516</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.199289768352338</v>
+        <v>276.5738825673489</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.227315643070162</v>
+        <v>541.167845511507</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>53.22906226641511</v>
@@ -6890,6 +7062,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>53.88647686964453</v>
+      </c>
+      <c r="W7" t="n">
+        <v>158.17338967292</v>
+      </c>
+      <c r="X7" t="n">
+        <v>274.2390544344365</v>
       </c>
     </row>
     <row r="8">
@@ -6908,10 +7086,10 @@
         <v>131.2214628321221</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.010769774893007</v>
+        <v>145.934763157738</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.036133815221473</v>
+        <v>305.8131375419835</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>66.04435652237277</v>
@@ -6960,6 +7138,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>72.85468745680132</v>
+      </c>
+      <c r="W8" t="n">
+        <v>88.9355323547114</v>
+      </c>
+      <c r="X8" t="n">
+        <v>157.3121050517687</v>
       </c>
     </row>
     <row r="9">
@@ -6978,10 +7162,10 @@
         <v>136.1200585562044</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.021353079015081</v>
+        <v>151.5035698395286</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.039787122658536</v>
+        <v>303.3786473154019</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>36.04605460649624</v>
@@ -7030,6 +7214,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>35.76713208410784</v>
+      </c>
+      <c r="W9" t="n">
+        <v>91.98627241058088</v>
+      </c>
+      <c r="X9" t="n">
+        <v>156.6381367062646</v>
       </c>
     </row>
     <row r="10">
@@ -7048,10 +7238,10 @@
         <v>123.0777938483221</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.992401877848456</v>
+        <v>136.6870094092204</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.97781011356031</v>
+        <v>214.4455523094579</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>560.2993113635969</v>
@@ -7100,6 +7290,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>683.8042433207072</v>
+      </c>
+      <c r="W10" t="n">
+        <v>83.84350782998811</v>
+      </c>
+      <c r="X10" t="n">
+        <v>117.3415435141877</v>
       </c>
     </row>
     <row r="11">
@@ -7118,10 +7314,10 @@
         <v>90.84783292746816</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.907611218998285</v>
+        <v>100.2278952561736</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1.912049794749575</v>
+        <v>109.6135735631875</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>124.2711634145906</v>
@@ -7170,6 +7366,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>122.2418878711609</v>
+      </c>
+      <c r="W11" t="n">
+        <v>63.40473856017664</v>
+      </c>
+      <c r="X11" t="n">
+        <v>68.21858054813588</v>
       </c>
     </row>
     <row r="12">
@@ -7188,10 +7390,10 @@
         <v>475.6166446524368</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.418043845374908</v>
+        <v>543.9985064148083</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.223977121357667</v>
+        <v>787.0602871231563</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>163.5507229305759</v>
@@ -7240,6 +7442,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>277.0567414731555</v>
+      </c>
+      <c r="W12" t="n">
+        <v>290.8855760689498</v>
+      </c>
+      <c r="X12" t="n">
+        <v>388.9017364240259</v>
       </c>
     </row>
     <row r="13">
@@ -7258,10 +7466,10 @@
         <v>137.3008427466518</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.023855250548123</v>
+        <v>152.8465647269913</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.935295445357621</v>
+        <v>361.152394173914</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>245.6862001803302</v>
@@ -7310,6 +7518,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>401.6981769955059</v>
+      </c>
+      <c r="W13" t="n">
+        <v>92.72031843302986</v>
+      </c>
+      <c r="X13" t="n">
+        <v>175.5077449530492</v>
       </c>
     </row>
     <row r="14">
@@ -7328,10 +7542,10 @@
         <v>304.3889985193259</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2.268308535570748</v>
+        <v>344.7830174723056</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2.30031387810577</v>
+        <v>857.4862245205563</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>249.2598774472341</v>
@@ -7380,6 +7594,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>274.5189432152974</v>
+      </c>
+      <c r="W14" t="n">
+        <v>192.9094902193581</v>
+      </c>
+      <c r="X14" t="n">
+        <v>398.7731713813679</v>
       </c>
     </row>
     <row r="15">
@@ -7398,10 +7618,10 @@
         <v>67.81478323443531</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.829367805577168</v>
+        <v>74.34147036847325</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.84032986439515</v>
+        <v>212.9757504641147</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>33.98849134059365</v>
@@ -7450,6 +7670,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>42.47474138804216</v>
+      </c>
+      <c r="W15" t="n">
+        <v>48.44624372378618</v>
+      </c>
+      <c r="X15" t="n">
+        <v>113.7580723413437</v>
       </c>
     </row>
     <row r="16">
@@ -7468,10 +7694,10 @@
         <v>100.9976422281052</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.936769695378661</v>
+        <v>111.683135042612</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.931489587955087</v>
+        <v>116.0427417312385</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>53.47979512001307</v>
@@ -7520,6 +7746,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>54.12960093161038</v>
+      </c>
+      <c r="W16" t="n">
+        <v>69.89558431312599</v>
+      </c>
+      <c r="X16" t="n">
+        <v>71.71229834977616</v>
       </c>
     </row>
     <row r="17">
@@ -7538,10 +7770,10 @@
         <v>65.92916907523437</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.821993919117797</v>
+        <v>72.22998071167444</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.839433090076003</v>
+        <v>110.6202611462784</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>38.38234241528252</v>
@@ -7590,6 +7822,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>38.53302950560662</v>
+      </c>
+      <c r="W17" t="n">
+        <v>47.20523047680616</v>
+      </c>
+      <c r="X17" t="n">
+        <v>66.62924255523933</v>
       </c>
     </row>
     <row r="18">
@@ -7608,10 +7846,10 @@
         <v>20.60629913270002</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.542426707515448</v>
+        <v>22.01068943454562</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.561294750439705</v>
+        <v>41.92758162087955</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>15.07517747610315</v>
@@ -7660,6 +7898,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>14.88502614028108</v>
+      </c>
+      <c r="W18" t="n">
+        <v>16.18813855308676</v>
+      </c>
+      <c r="X18" t="n">
+        <v>27.45670287842556</v>
       </c>
     </row>
     <row r="19">
@@ -7678,10 +7922,10 @@
         <v>21.00217458215732</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.546636407292474</v>
+        <v>22.44284957640871</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.565985118979595</v>
+        <v>43.65189164395604</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>12.03947360007721</v>
@@ -7730,6 +7974,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>11.03550640396157</v>
+      </c>
+      <c r="W19" t="n">
+        <v>16.47411256574711</v>
+      </c>
+      <c r="X19" t="n">
+        <v>28.38105109133995</v>
       </c>
     </row>
     <row r="20">
@@ -7748,10 +7998,10 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>14.61038961038961</v>
@@ -7800,6 +8050,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>13.78907039428072</v>
+      </c>
+      <c r="W20" t="n">
+        <v>8.322258123435352</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.322258123435352</v>
       </c>
     </row>
     <row r="21">
@@ -7818,10 +8074,10 @@
         <v>14.36294379407374</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.464712067662454</v>
+        <v>15.22163111138705</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.389743963354619</v>
+        <v>30.52861938538214</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>47.52855886458278</v>
@@ -7870,6 +8126,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>1019.755012995979</v>
+      </c>
+      <c r="W21" t="n">
+        <v>11.6129642773251</v>
+      </c>
+      <c r="X21" t="n">
+        <v>19.55375571375</v>
       </c>
     </row>
     <row r="22">
@@ -7888,10 +8150,10 @@
         <v>14.47911226566293</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.466403022283111</v>
+        <v>15.34743855512961</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.478879268940024</v>
+        <v>33.85698484918524</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>14.95693718745309</v>
@@ -7940,6 +8202,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>14.54977121954716</v>
+      </c>
+      <c r="W22" t="n">
+        <v>11.69937146537998</v>
+      </c>
+      <c r="X22" t="n">
+        <v>21.51396478035683</v>
       </c>
     </row>
     <row r="23">
@@ -7958,10 +8226,10 @@
         <v>14.49740670372631</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.466668256932992</v>
+        <v>15.36725296668693</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1.466496696494247</v>
+        <v>26.43707994906483</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>17.85074670895786</v>
@@ -8010,6 +8278,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>17.941415846944</v>
+      </c>
+      <c r="W23" t="n">
+        <v>11.71297398809445</v>
+      </c>
+      <c r="X23" t="n">
+        <v>18.00571560239192</v>
       </c>
     </row>
     <row r="24">
@@ -8028,10 +8302,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>6.67641459982895</v>
@@ -8080,6 +8354,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>5.835162046220703</v>
+      </c>
+      <c r="W24" t="n">
+        <v>8.322258123435352</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.322258123435352</v>
       </c>
     </row>
     <row r="25">
@@ -8098,10 +8378,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1.390689708946192</v>
+        <v>10.51456250439393</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>12.98701298701298</v>
@@ -8151,6 +8431,12 @@
       <c r="V25" s="2" t="n">
         <v>12.66259887840875</v>
       </c>
+      <c r="W25" t="n">
+        <v>8.322258123435352</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8.322258123435351</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -8219,6 +8505,12 @@
         <v>1</v>
       </c>
       <c r="V26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8691,7 +8983,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.122835645497551</v>
       </c>
@@ -8817,7 +9108,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>East_China_Sea (1997)</t>
@@ -8881,7 +9171,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -8921,7 +9210,6 @@
       <c r="AP3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
@@ -9073,7 +9361,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.1337878841345435</v>
       </c>
@@ -9175,7 +9462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9236,14 +9523,12 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>2819.964</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9257,14 +9542,12 @@
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>2819.964</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9278,14 +9561,12 @@
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>2819.964</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -9709,6 +9990,50 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2819.964</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2819.964</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9845,7 +10170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9881,7 +10206,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9894,7 +10218,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9907,7 +10230,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -9920,7 +10242,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -9933,7 +10254,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -9946,7 +10266,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -9959,7 +10278,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -9972,7 +10290,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -9985,7 +10302,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -10029,7 +10345,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10046,7 +10362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10322,6 +10638,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
